--- a/_Rarzrabotki/Письмо Директору по отчетам на производство/19082026/Звіт з виконання СС на 19-08-2026.xlsx
+++ b/_Rarzrabotki/Письмо Директору по отчетам на производство/19082026/Звіт з виконання СС на 19-08-2026.xlsx
@@ -62,18 +62,15 @@
     <t>МД IRC 2026</t>
   </si>
   <si>
-    <t>Дополнительная Комплектация</t>
-  </si>
-  <si>
-    <t>монжа кондиціонеру</t>
-  </si>
-  <si>
     <t>Каркас</t>
   </si>
   <si>
     <t>Влаштування підшиви модуля</t>
   </si>
   <si>
+    <t>Грунтування металокаркасу</t>
+  </si>
+  <si>
     <t>Збирання деталей</t>
   </si>
   <si>
@@ -141,6 +138,9 @@
   </si>
   <si>
     <t>Фасад</t>
+  </si>
+  <si>
+    <t>Гідроізоляційна плівка</t>
   </si>
   <si>
     <t>монтаж обрешітки по каркасу</t>
@@ -586,13 +586,13 @@
         <v>3270</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2647.29</v>
+        <v>2952.63</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>622.71</v>
+        <v>317.37</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>81</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="11" ht="11" customHeight="true" outlineLevel="1">
@@ -628,7 +628,7 @@
       <c r="D13" s="25" t="e"/>
       <c r="E13" s="17" t="e"/>
       <c r="F13" s="26" t="n">
-        <v>6</v>
+        <v>966.69</v>
       </c>
       <c r="G13" s="18" t="e"/>
       <c r="H13" s="17" t="e"/>
@@ -642,24 +642,24 @@
       <c r="D14" s="27" t="e"/>
       <c r="E14" s="23" t="e"/>
       <c r="F14" s="28" t="n">
-        <v>6</v>
+        <v>143.97</v>
       </c>
       <c r="G14" s="24" t="e"/>
       <c r="H14" s="23" t="e"/>
     </row>
-    <row r="15" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A15" s="25" t="s">
+    <row r="15" ht="11" customHeight="true" outlineLevel="2">
+      <c r="A15" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="e"/>
-      <c r="C15" s="25" t="e"/>
-      <c r="D15" s="25" t="e"/>
-      <c r="E15" s="17" t="e"/>
-      <c r="F15" s="26" t="n">
-        <v>775.35</v>
-      </c>
-      <c r="G15" s="18" t="e"/>
-      <c r="H15" s="17" t="e"/>
+      <c r="B15" s="27" t="e"/>
+      <c r="C15" s="27" t="e"/>
+      <c r="D15" s="27" t="e"/>
+      <c r="E15" s="23" t="e"/>
+      <c r="F15" s="28" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="G15" s="24" t="e"/>
+      <c r="H15" s="23" t="e"/>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="2">
       <c r="A16" s="27" t="s">
@@ -670,7 +670,7 @@
       <c r="D16" s="27" t="e"/>
       <c r="E16" s="23" t="e"/>
       <c r="F16" s="28" t="n">
-        <v>133.69</v>
+        <v>143.97</v>
       </c>
       <c r="G16" s="24" t="e"/>
       <c r="H16" s="23" t="e"/>
@@ -684,7 +684,7 @@
       <c r="D17" s="27" t="e"/>
       <c r="E17" s="23" t="e"/>
       <c r="F17" s="28" t="n">
-        <v>131.63</v>
+        <v>133.69</v>
       </c>
       <c r="G17" s="24" t="e"/>
       <c r="H17" s="23" t="e"/>
@@ -698,7 +698,7 @@
       <c r="D18" s="27" t="e"/>
       <c r="E18" s="23" t="e"/>
       <c r="F18" s="28" t="n">
-        <v>131.63</v>
+        <v>143.97</v>
       </c>
       <c r="G18" s="24" t="e"/>
       <c r="H18" s="23" t="e"/>
@@ -712,7 +712,7 @@
       <c r="D19" s="27" t="e"/>
       <c r="E19" s="23" t="e"/>
       <c r="F19" s="28" t="n">
-        <v>143.97</v>
+        <v>154.29</v>
       </c>
       <c r="G19" s="24" t="e"/>
       <c r="H19" s="23" t="e"/>
@@ -726,38 +726,38 @@
       <c r="D20" s="27" t="e"/>
       <c r="E20" s="23" t="e"/>
       <c r="F20" s="28" t="n">
-        <v>111.03</v>
+        <v>123.4</v>
       </c>
       <c r="G20" s="24" t="e"/>
       <c r="H20" s="23" t="e"/>
     </row>
-    <row r="21" ht="11" customHeight="true" outlineLevel="2">
-      <c r="A21" s="27" t="s">
+    <row r="21" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A21" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="27" t="e"/>
-      <c r="C21" s="27" t="e"/>
-      <c r="D21" s="27" t="e"/>
-      <c r="E21" s="23" t="e"/>
-      <c r="F21" s="28" t="n">
-        <v>123.4</v>
-      </c>
-      <c r="G21" s="24" t="e"/>
-      <c r="H21" s="23" t="e"/>
-    </row>
-    <row r="22" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A22" s="25" t="s">
+      <c r="B21" s="25" t="e"/>
+      <c r="C21" s="25" t="e"/>
+      <c r="D21" s="25" t="e"/>
+      <c r="E21" s="17" t="e"/>
+      <c r="F21" s="26" t="n">
+        <v>168</v>
+      </c>
+      <c r="G21" s="18" t="e"/>
+      <c r="H21" s="17" t="e"/>
+    </row>
+    <row r="22" ht="11" customHeight="true" outlineLevel="2">
+      <c r="A22" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="25" t="e"/>
-      <c r="C22" s="25" t="e"/>
-      <c r="D22" s="25" t="e"/>
-      <c r="E22" s="17" t="e"/>
-      <c r="F22" s="26" t="n">
-        <v>168</v>
-      </c>
-      <c r="G22" s="18" t="e"/>
-      <c r="H22" s="17" t="e"/>
+      <c r="B22" s="27" t="e"/>
+      <c r="C22" s="27" t="e"/>
+      <c r="D22" s="27" t="e"/>
+      <c r="E22" s="23" t="e"/>
+      <c r="F22" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="G22" s="24" t="e"/>
+      <c r="H22" s="23" t="e"/>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="2">
       <c r="A23" s="27" t="s">
@@ -768,7 +768,7 @@
       <c r="D23" s="27" t="e"/>
       <c r="E23" s="23" t="e"/>
       <c r="F23" s="28" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G23" s="24" t="e"/>
       <c r="H23" s="23" t="e"/>
@@ -782,38 +782,38 @@
       <c r="D24" s="27" t="e"/>
       <c r="E24" s="23" t="e"/>
       <c r="F24" s="28" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="G24" s="24" t="e"/>
       <c r="H24" s="23" t="e"/>
     </row>
-    <row r="25" ht="11" customHeight="true" outlineLevel="2">
-      <c r="A25" s="27" t="s">
+    <row r="25" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A25" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="27" t="e"/>
-      <c r="C25" s="27" t="e"/>
-      <c r="D25" s="27" t="e"/>
-      <c r="E25" s="23" t="e"/>
-      <c r="F25" s="28" t="n">
-        <v>96</v>
-      </c>
-      <c r="G25" s="24" t="e"/>
-      <c r="H25" s="23" t="e"/>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A26" s="25" t="s">
+      <c r="B25" s="25" t="e"/>
+      <c r="C25" s="25" t="e"/>
+      <c r="D25" s="25" t="e"/>
+      <c r="E25" s="17" t="e"/>
+      <c r="F25" s="16" t="n">
+        <v>1284</v>
+      </c>
+      <c r="G25" s="18" t="e"/>
+      <c r="H25" s="17" t="e"/>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="2">
+      <c r="A26" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="25" t="e"/>
-      <c r="C26" s="25" t="e"/>
-      <c r="D26" s="25" t="e"/>
-      <c r="E26" s="17" t="e"/>
-      <c r="F26" s="16" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G26" s="18" t="e"/>
-      <c r="H26" s="17" t="e"/>
+      <c r="B26" s="27" t="e"/>
+      <c r="C26" s="27" t="e"/>
+      <c r="D26" s="27" t="e"/>
+      <c r="E26" s="23" t="e"/>
+      <c r="F26" s="28" t="n">
+        <v>144</v>
+      </c>
+      <c r="G26" s="24" t="e"/>
+      <c r="H26" s="23" t="e"/>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="2">
       <c r="A27" s="27" t="s">
@@ -824,7 +824,7 @@
       <c r="D27" s="27" t="e"/>
       <c r="E27" s="23" t="e"/>
       <c r="F27" s="28" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="G27" s="24" t="e"/>
       <c r="H27" s="23" t="e"/>
@@ -838,7 +838,7 @@
       <c r="D28" s="27" t="e"/>
       <c r="E28" s="23" t="e"/>
       <c r="F28" s="28" t="n">
-        <v>144</v>
+        <v>360</v>
       </c>
       <c r="G28" s="24" t="e"/>
       <c r="H28" s="23" t="e"/>
@@ -852,7 +852,7 @@
       <c r="D29" s="27" t="e"/>
       <c r="E29" s="23" t="e"/>
       <c r="F29" s="28" t="n">
-        <v>360</v>
+        <v>156</v>
       </c>
       <c r="G29" s="24" t="e"/>
       <c r="H29" s="23" t="e"/>
@@ -894,38 +894,38 @@
       <c r="D32" s="27" t="e"/>
       <c r="E32" s="23" t="e"/>
       <c r="F32" s="28" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="G32" s="24" t="e"/>
       <c r="H32" s="23" t="e"/>
     </row>
-    <row r="33" ht="11" customHeight="true" outlineLevel="2">
-      <c r="A33" s="27" t="s">
+    <row r="33" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A33" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="27" t="e"/>
-      <c r="C33" s="27" t="e"/>
-      <c r="D33" s="27" t="e"/>
-      <c r="E33" s="23" t="e"/>
-      <c r="F33" s="28" t="n">
-        <v>156</v>
-      </c>
-      <c r="G33" s="24" t="e"/>
-      <c r="H33" s="23" t="e"/>
-    </row>
-    <row r="34" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A34" s="25" t="s">
+      <c r="B33" s="25" t="e"/>
+      <c r="C33" s="25" t="e"/>
+      <c r="D33" s="25" t="e"/>
+      <c r="E33" s="17" t="e"/>
+      <c r="F33" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="G33" s="18" t="e"/>
+      <c r="H33" s="17" t="e"/>
+    </row>
+    <row r="34" ht="11" customHeight="true" outlineLevel="2">
+      <c r="A34" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="25" t="e"/>
-      <c r="C34" s="25" t="e"/>
-      <c r="D34" s="25" t="e"/>
-      <c r="E34" s="17" t="e"/>
-      <c r="F34" s="26" t="n">
-        <v>96</v>
-      </c>
-      <c r="G34" s="18" t="e"/>
-      <c r="H34" s="17" t="e"/>
+      <c r="B34" s="27" t="e"/>
+      <c r="C34" s="27" t="e"/>
+      <c r="D34" s="27" t="e"/>
+      <c r="E34" s="23" t="e"/>
+      <c r="F34" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="G34" s="24" t="e"/>
+      <c r="H34" s="23" t="e"/>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="2">
       <c r="A35" s="27" t="s">
@@ -969,33 +969,33 @@
       <c r="G37" s="24" t="e"/>
       <c r="H37" s="23" t="e"/>
     </row>
-    <row r="38" ht="11" customHeight="true" outlineLevel="2">
-      <c r="A38" s="27" t="s">
+    <row r="38" ht="11" customHeight="true" outlineLevel="1">
+      <c r="A38" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="27" t="e"/>
-      <c r="C38" s="27" t="e"/>
-      <c r="D38" s="27" t="e"/>
-      <c r="E38" s="23" t="e"/>
-      <c r="F38" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="G38" s="24" t="e"/>
-      <c r="H38" s="23" t="e"/>
-    </row>
-    <row r="39" ht="11" customHeight="true" outlineLevel="1">
-      <c r="A39" s="25" t="s">
+      <c r="B38" s="25" t="e"/>
+      <c r="C38" s="25" t="e"/>
+      <c r="D38" s="25" t="e"/>
+      <c r="E38" s="17" t="e"/>
+      <c r="F38" s="26" t="n">
+        <v>432</v>
+      </c>
+      <c r="G38" s="18" t="e"/>
+      <c r="H38" s="17" t="e"/>
+    </row>
+    <row r="39" ht="11" customHeight="true" outlineLevel="2">
+      <c r="A39" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="25" t="e"/>
-      <c r="C39" s="25" t="e"/>
-      <c r="D39" s="25" t="e"/>
-      <c r="E39" s="17" t="e"/>
-      <c r="F39" s="26" t="n">
-        <v>360</v>
-      </c>
-      <c r="G39" s="18" t="e"/>
-      <c r="H39" s="17" t="e"/>
+      <c r="B39" s="27" t="e"/>
+      <c r="C39" s="27" t="e"/>
+      <c r="D39" s="27" t="e"/>
+      <c r="E39" s="23" t="e"/>
+      <c r="F39" s="28" t="n">
+        <v>72</v>
+      </c>
+      <c r="G39" s="24" t="e"/>
+      <c r="H39" s="23" t="e"/>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="2">
       <c r="A40" s="27" t="s">
@@ -1092,13 +1092,13 @@
         <v>3270</v>
       </c>
       <c r="F46" s="30" t="n">
-        <v>2647.29</v>
+        <v>2952.63</v>
       </c>
       <c r="G46" s="31" t="n">
-        <v>622.71</v>
+        <v>317.37</v>
       </c>
       <c r="H46" s="32" t="n">
-        <v>81</v>
+        <v>90.3</v>
       </c>
     </row>
   </sheetData>
